--- a/отчеты для СН/всякие/08,26/27,08,26/Бердянск/прих маш тн пок 27,08,26 Бердянск.xlsx
+++ b/отчеты для СН/всякие/08,26/27,08,26/Бердянск/прих маш тн пок 27,08,26 Бердянск.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\отчеты для СН\всякие\08,26\27,08,26\Бердянск\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EB6765-DB26-40F7-8D9B-708F2D090093}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685AF9BC-E1E0-425C-92D7-0C35891BBCC9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="КИ" sheetId="5" r:id="rId1"/>
     <sheet name="ЗПФ" sheetId="6" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
